--- a/engine/amoc_study/AMOC_Valuation_Model_10092026_public.xlsx
+++ b/engine/amoc_study/AMOC_Valuation_Model_10092026_public.xlsx
@@ -40540,7 +40540,7 @@
         </is>
       </c>
     </row>
-    <row r="180" ht="100" customHeight="1">
+    <row r="180" ht="110" customHeight="1">
       <c r="A180" s="7" t="inlineStr">
         <is>
           <t>Terminal real risk-free rate</t>
@@ -40561,7 +40561,7 @@
       </c>
       <c r="E180" s="4" t="inlineStr">
         <is>
-          <t>Terminal real risk-free rate, READ LIVE from the house macro path (engine/macro_paths/EG.json) rather than typed here. The terminal NOMINAL risk-free rate is not an input either: it is the house path's own `terminal_rf`, which is this real rate plus the central bank's inflation target in force for the terminal horizon, so the single most terminal-value-sensitive number in the model can be set neither by hand nor by this study alone. TWO EDITIONS OF THIS LINE ARE RETIRED. The first hardcoded 10.50% by adding 5.5pp to the 5% target dated Q4-2028 while describing it as 'the' medium-term target. The second, adopted 06-Aug-2026, derived the rate correctly but from a real convention typed into this file, so when the house convention moved from 5.5% to 3.5% — the retired figure being a restrictive policy stance rather than a long-run real rate — this study went on discounting at 12.50% while every conformed study discounted at 10.50%. Two readers of one economy must not disagree</t>
+          <t>Terminal real risk-free rate. It is NOT set by this study: it is read from the single long-run view of the Egyptian economy that every study in this book discounts on, so one company cannot quietly hold a different one. The terminal NOMINAL risk-free rate is not an input either — it is that same shared view's own figure, this real rate plus the central bank's inflation target in force for the terminal horizon — so the single most terminal-value-sensitive number in the model can be set neither by hand nor by this study alone. TWO EDITIONS OF THIS LINE ARE RETIRED. The first hardcoded 10.50% by adding 5.5pp to the 5% target dated Q4-2028 while describing it as 'the' medium-term target. The second, adopted 06-Aug-2026, derived the rate correctly but from a real convention typed into this file, so when the house convention moved from 5.5% to 3.5% — the retired figure being a restrictive policy stance rather than a long-run real rate — this study went on discounting at 12.50% while every conformed study discounted at 10.50%. Two readers of one economy must not disagree</t>
         </is>
       </c>
     </row>
